--- a/data.xlsx
+++ b/data.xlsx
@@ -1040,7 +1040,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>3</v>
@@ -1413,20 +1413,20 @@
       <c r="S2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1879,322 +1879,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_lvrbvtr1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_lvrbvtr1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u_lin_pusk_lvrbvtr1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u2_pusk_lvrbvtr1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_lvrbvtr1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>neispr_zn_lvrbvtr1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_lvrbvtr2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_lvrbvtr2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u_lin_pusk_lvrbvtr2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u2_pusk_lvrbvtr2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_lvrbvtr2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>neispr_zn_lvrbvtr2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vvod_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzA_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzB_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzC_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>gen_pusk_ptoc_lvttoc</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srabsign_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srab_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_A_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_C_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzA_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzB_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzC_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>gen_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srabsign_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srab_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_A_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_C_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzA_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzB_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzC_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>gen_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srabsign_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srab_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_A_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_C_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>kpon_pusk_ptuv1_lvttoc</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>kpon_pusk_ptuv2_lvttoc</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ia_start_out_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ib_start_out_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ic_start_out_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>start_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>blok_rblc1_lvttoc</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_pusk_lvttoc</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_ptrc1</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_ptrc1</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_ptrc1</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_ptrc1</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rblc1</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rblc1</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>zapret_rblc1</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rbre1</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rbre1</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>zapret_rbre1</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_lvalv</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -809,8 +809,8 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="2" t="n">
-        <v>1</v>
+      <c r="W2" t="n">
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>3</v>
@@ -1048,23 +1048,23 @@
       <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>40</v>
@@ -1079,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0.4</v>
@@ -1090,8 +1090,8 @@
       <c r="Q2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
+      <c r="R2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>40</v>
@@ -1099,8 +1099,8 @@
       <c r="T2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
+      <c r="U2" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1395,8 +1395,8 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>5</v>
+      <c r="N2" t="n">
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1413,20 +1413,20 @@
       <c r="S2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="T2" s="2" t="n">
-        <v>1</v>
+      <c r="T2" t="n">
+        <v>0</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
